--- a/data/seed/portfolio/L-2024-9708/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-9708/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>47976000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>8158000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Bekobod Plastik AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>328991598</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000589205515001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №262/26 от 06.07.2026</t>
+          <t>Оплата за сырье по договору №3/26 от 01.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,23 +599,23 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>23863000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>46756000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -625,14 +625,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №53/26 от 06.07.2026</t>
+          <t>Предоплата за материалы по договору №285/26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>11776000</v>
+        <v>21264000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chust Sut AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>299289915</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000855892055001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3971 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №2380 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,38 +683,38 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>5768000</v>
+        <v>3068000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lazzat Sut MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>356521849</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000365559353001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1030 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №218/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -724,38 +724,38 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>3174000</v>
+        <v>12960000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>356876449</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000968329370001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №298/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №25/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>1828000</v>
+        <v>5903000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9547 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №235/26 от 03.07.2026</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>1788000</v>
+        <v>28290000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Navro'z Logistik MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>251983633</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000027244948001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №125/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №9050 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -845,23 +845,23 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>2461000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>10106000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>356876449</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000968329370001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №194/26</t>
+          <t>Оплата за товар по счет-фактуре №8340 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -886,33 +886,33 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>3489000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>2991000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bekobod Tikuv MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>313731901</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000075161529001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №124/26</t>
+          <t>Оплата за товар по счет-фактуре №5886 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>11007000</v>
+        <v>8062000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Denov Trans Servis MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>303480905</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000823043299001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №75/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №146/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -969,34 +969,39 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>19178000</v>
+        <v>15817000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Ziyo Mebel XK</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>304179873</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000072850583001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за упаковочные материалы, с/ф №9099</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1004,40 +1009,40 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>5785000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>17904000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №145/26 от 09.07.2026</t>
+          <t>Предоплата за материалы по дог. №108/26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,40 +1050,35 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>4018000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>19178000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>331743410</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №57/26, НДС 12%</t>
+          <t>ПЕРЕЧИСЛЕНИЕ ЗАРАБОТНОЙ ПЛАТЫ ЗА ИЮНЬ 2026 Г. СОГЛАСНО РЕЕСТРУ №21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1087,39 +1087,39 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2358000</v>
+        <v>61544000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>228532391</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000990517963001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №19/21</t>
+          <t>Предоплата за материалы по договору №212/26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1128,39 +1128,39 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2861000</v>
+        <v>2358000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ilhom Yog' Zavodi AJ</t>
+          <t>Navoiy Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>273640014</t>
+          <t>237319010</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000841541261001</t>
+          <t>20208000751615296001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №166/26</t>
+          <t>Аренда помещения за июль, дог. №29/22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1170,38 +1170,38 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>15675000</v>
+        <v>5714000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2396 за поставленный товар</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2776 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1211,38 +1211,38 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>15070000</v>
+        <v>5003000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №269/26 от 13.07.2026</t>
+          <t>Оплата за товар по с/ф №8003 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,33 +1250,33 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>14106000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>8556000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Bekobod Plastik AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>328991598</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000589205515001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3535 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №234/26</t>
         </is>
       </c>
     </row>
@@ -1293,21 +1293,21 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>11528000</v>
+        <v>6428000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №124/26, НДС 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №128/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1334,21 +1334,21 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>2384000</v>
+        <v>4643000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8431 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №5527 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1373,33 +1373,33 @@
           <t>120</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>4135000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>3881000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №2506</t>
+          <t>Оплата за продукцию по договору №229/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1414,23 +1414,23 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>17917000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>3079000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4644</t>
+          <t>Предоплата за товар по дог. №42/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
@@ -1456,32 +1456,32 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>43903000</v>
+        <v>61092000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №233/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8627</t>
         </is>
       </c>
     </row>
@@ -1498,31 +1498,31 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>17054000</v>
+        <v>22622000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro Servis MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>248568764</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000959683293001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2354 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №171/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1537,33 +1537,33 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>12739000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>2615000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8028 от 14.07.2026, в т.ч. НДС 12%</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
     </row>
@@ -1578,40 +1578,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>3699000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>2615000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4706 за поставленный товар</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1621,38 +1621,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>2513000</v>
+        <v>19422000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №43/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1662,38 +1662,38 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>6422000</v>
+        <v>7584000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4841 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №3465 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1701,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>51723000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>21707000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Denov Trans Servis MChJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>303480905</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000823043299001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №191/26</t>
+          <t>Оплата по счет-фактуре №3105 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1744,38 +1744,38 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>2889000</v>
+        <v>7703000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5655 от 16.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №188/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1783,40 +1783,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>2615000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>11670000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Предоплата за товар по договору №4/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>2615000</v>
+        <v>3890000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
@@ -1850,14 +1850,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1865,23 +1865,23 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>4889000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>48058000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut Mahsulotlari MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>359150945</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000608236593001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1891,14 +1891,14 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6995</t>
+          <t>Оплата по счет-фактуре №101 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1906,40 +1906,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>26504000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>5780000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
+          <t>Yulduz Tekstil MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>255201724</t>
+          <t>298363380</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000143254582001</t>
+          <t>20208000724494826001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №4187</t>
+          <t>Оплата по с/ф №8463 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1947,23 +1947,23 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>34293000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>6628000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1973,14 +1973,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №237/26</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8609 ОТ 23.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1990,21 +1990,21 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>3307000</v>
+        <v>6105000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2014,14 +2014,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №64/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №137/26 от 23.07.2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2031,38 +2031,38 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>7691000</v>
+        <v>4934000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>356876449</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000968329370001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №150/26 от 20.07.2026</t>
+          <t>Оплата за товар по с/ф №5813 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2072,21 +2072,21 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>4210000</v>
+        <v>7587000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2096,14 +2096,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №3690 ОТ 20.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №170/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2113,38 +2113,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>3835000</v>
+        <v>2656000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>356876449</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000968329370001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №164/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №3388 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>25.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2152,40 +2152,35 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>3452000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>275041798</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9708)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>16307000352556491417</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8931 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-9708 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2195,38 +2190,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>2687000</v>
+        <v>5697000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Yulduz Tekstil MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>298363380</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000724494826001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4673 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №110/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2236,21 +2231,21 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>2559000</v>
+        <v>4495000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2260,14 +2255,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4660 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №3330 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2275,40 +2270,40 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>3154000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>3657000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТРИАЛЫ, С/Ф №6659</t>
+          <t>Оплата за продукцию по договору №296/26, НС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2316,40 +2311,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>16120000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>3044000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Yulduz Tekstil MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>298363380</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000724494826001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №216/26</t>
+          <t>Оплата за товар по с/ф №7080 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2358,39 +2353,39 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>2207000</v>
+        <v>1474000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000846034809001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №5105</t>
+          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2399,39 +2394,39 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>30548000</v>
+        <v>6270000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Ziyo Mebel XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>304179873</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000072850583001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №50</t>
+          <t>Предоплата за материалы по договору №20/26</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2441,38 +2436,38 @@
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>14674000</v>
+        <v>10841000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1143 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №1320 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2480,40 +2475,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>7032000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>6476000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Bekobod Plastik AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>328991598</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000589205515001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №263/26 от 22.07.2026</t>
+          <t>Оплата за транспортные услуги по дог. №271/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2521,40 +2516,40 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>3963000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>4136000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №8004 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2564,21 +2559,21 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>9533000</v>
+        <v>4029000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2588,14 +2583,14 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №207/26 от 24.07.2026</t>
+          <t>Оплата за продукцию по договору №166/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2605,38 +2600,38 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>3931000</v>
+        <v>2505000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №470 от 24.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4747 от 31.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>25.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2645,17 +2640,17 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>17000000</v>
+        <v>300000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9708)</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>16307000352556491417</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2665,14 +2660,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9708 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2680,23 +2675,23 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>10689000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>8388000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2706,14 +2701,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4834</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №29/26</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2721,40 +2716,40 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>7017000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>9959000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Navro'z Logistik MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>251983633</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000027244948001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №107/26 ОТ 27.07.2026</t>
+          <t>Предоплата за материалы по договору №101/26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2763,39 +2758,39 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>1474000</v>
+        <v>12219000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ziyo Mebel XK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>304179873</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000566813144001</t>
+          <t>20208000072850583001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №4965</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2805,21 +2800,21 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>14111000</v>
+        <v>45303000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2829,14 +2824,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №2615 28.07.2026, QQS BILAN</t>
+          <t>Shartnoma №49/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2846,38 +2841,38 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>5154000</v>
+        <v>4192000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Shartnoma №154/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №6361 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2886,39 +2881,34 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>7292000</v>
+        <v>20341000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>255201724</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000143254582001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2079</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №541</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2927,39 +2917,39 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>11572000</v>
+        <v>48333000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3808</t>
+          <t>Оплата за упаковочные материалы, с/ф №5304</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2967,40 +2957,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>8595000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>15403000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Bekobod Plastik AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>328991598</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000589205515001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №173/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №72/26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3010,21 +3000,21 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>4321000</v>
+        <v>67781000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3034,14 +3024,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №259/26 от 30.07.2026</t>
+          <t>Оплата за товар по с/ф №7507 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3051,21 +3041,21 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>2197000</v>
+        <v>18924000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3075,14 +3065,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №35/26 от 30.07.2026</t>
+          <t>Оплата по с/ф №632 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3090,40 +3080,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>1856000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>2501000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro Servis MChJ</t>
+          <t>Navoiy Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>248568764</t>
+          <t>237319010</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000959683293001</t>
+          <t>20208000751615296001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №17/26 от 30.07.2026</t>
+          <t>Аренда помещения за август, дог. №29/22</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3132,39 +3122,39 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>2193000</v>
+        <v>9122000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bekobod Tikuv MChJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>313731901</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000075161529001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №316</t>
+          <t>Оплата за сырье по договору №162/26 от 11.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3172,40 +3162,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>2914000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>4735000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>255201724</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000143254582001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №181/26 ОТ 30.07.2026, НДС 12%</t>
+          <t>Оплата по с/ф №5284 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3215,38 +3205,38 @@
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>3314000</v>
+        <v>12397000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2894 от 1.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №266/26 от 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3254,35 +3244,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>5681000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Omad Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Mahsulot uchun to'lov, shartnoma №34/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3290,40 +3285,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>4500000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>2774000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №281/26, НДС 12%</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3331,40 +3326,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>7042000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>2774000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №33 за поставленный товар</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3373,34 +3368,39 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>20341000</v>
+        <v>15950000</v>
       </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Sharq Un Mahsulotlari XK</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №4316</t>
+          <t>Оплата за транспортные услуги по договору №60/26</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3409,39 +3409,39 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>7725000</v>
+        <v>24384000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2873</t>
+          <t>Transport xizmatlari uchun to'lov, shart. №252/26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,40 +3449,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>24732000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>12742000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №257/26</t>
+          <t>Оплата за товар по с/ф №8875 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,40 +3490,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>9345000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>19584000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Bekobod Plastik AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>328991598</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000589205515001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №170/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №3/26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3533,38 +3533,38 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>4974000</v>
+        <v>7007000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1581 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №89/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3572,40 +3572,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>3661000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>4130000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №109/26 от 10.08.2026</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3614,39 +3614,39 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2501000</v>
+        <v>39459000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>228532391</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000990517963001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>BINO IJARASI UCHUN TO'LOV AVGUST</t>
+          <t>Оплата за упаковочные материалы, с/ф №3128</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3655,22 +3655,22 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>7301000</v>
+        <v>55168000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut Mahsulotlari MChJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>359150945</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000608236593001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №211/26 от 10.08.2026, НДС 12%</t>
+          <t>Оплата за сырье по дог. №189/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3696,39 +3696,39 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>13611000</v>
+        <v>58555000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №158/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №159/26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3737,39 +3737,39 @@
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>15118000</v>
+        <v>1563000</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Angren Mehmonxona AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>394753331</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000158343630001</t>
+          <t>20208000846034809001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №74/26 от 11.08.2026, НДС 12%</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3778,39 +3778,34 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>10884000</v>
+        <v>17000000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>255201724</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9708)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000143254582001</t>
+          <t>16307000352556491417</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №86/26 от 12.08.2026, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-9708 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3820,21 +3815,21 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>38908000</v>
+        <v>58461000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3844,14 +3839,14 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №227/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №289/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3861,38 +3856,38 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>10987000</v>
+        <v>28778000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro Servis MChJ</t>
+          <t>Yulduz Tekstil MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>248568764</t>
+          <t>298363380</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000959683293001</t>
+          <t>20208000724494826001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №100/26 от 13.08.2026</t>
+          <t>Оплата за товар по с/ф №3450 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3902,21 +3897,21 @@
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>2600000</v>
+        <v>41586000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3926,14 +3921,14 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №40/26 от 13.08.2026</t>
+          <t>Оплата за товар по с/ф №8965 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3941,40 +3936,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>14497000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>25948000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №197/26</t>
+          <t>Tovar uchun o'lov, hisob-faktura №7208 28.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3984,21 +3979,21 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>19701000</v>
+        <v>5345000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4008,14 +4003,14 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №124 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №3310 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4025,38 +4020,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>9004000</v>
+        <v>5247000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Navro'z Logistik MChJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>251983633</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000027244948001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №140/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №57/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4065,39 +4060,34 @@
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>2774000</v>
+        <v>300000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4105,40 +4095,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>2774000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>5083000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮЛЬ 2026 Г.</t>
+          <t>Предоплата за товар по договору №194/26 от 01.09.2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4147,22 +4137,22 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>31924000</v>
+        <v>20630000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bekobod Tikuv MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>313731901</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000075161529001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4172,14 +4162,14 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №184/26</t>
+          <t>Оплата за транспортные услуги по договору №263/26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4189,21 +4179,21 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>27337000</v>
+        <v>3343000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4213,14 +4203,14 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7220 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №5773 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4230,21 +4220,21 @@
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>19676000</v>
+        <v>51677000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4254,14 +4244,14 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4249</t>
+          <t>Mahsulot uchun to'lov, shartnoma №287/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4271,38 +4261,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>4075000</v>
+        <v>23539000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7460 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №97/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4310,40 +4300,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>11531000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>7799000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Denov Trans Servis MChJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>303480905</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000823043299001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №41/26</t>
+          <t>Оплата по счет-фактуре №7496 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4351,23 +4341,23 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>21196000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>7718000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4377,14 +4367,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9591</t>
+          <t>Оплата за товар по счет-фактуре №340 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4392,23 +4382,23 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>47737000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>4218000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Tong Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>274341085</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000343611455001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4418,14 +4408,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по до. №204/26</t>
+          <t>Оплата за товар по счет-фактуре №3244 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4433,40 +4423,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n">
-        <v>4025000</v>
-      </c>
+      <c r="C105" s="2" t="n">
+        <v>14188000</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар подоговору №84/26 от 18.08.2026</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №8455</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4476,38 +4466,38 @@
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>2546000</v>
+        <v>5670000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3793 18.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №2924 за поствленный товар</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4515,40 +4505,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>15179000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>2813000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №259/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1450 07.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4558,21 +4548,21 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>4801000</v>
+        <v>2630000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4582,14 +4572,14 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №234/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4597,40 +4587,40 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>7363000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>2172000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Denov Trans Servis MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>303480905</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000823043299001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №193/26</t>
+          <t>Оплата за продукцию по дог. №260/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4640,21 +4630,21 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>7895000</v>
+        <v>2120000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4664,14 +4654,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1188 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №41/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4680,22 +4670,17 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>5340000</v>
+        <v>20136000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Denov Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>303480905</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000823043299001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4705,14 +4690,14 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №147/26</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №4009</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4720,40 +4705,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>7886000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>38277000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Shartnoma №75/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №22/26</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4763,38 +4748,38 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>7772000</v>
+        <v>9119000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro Servis MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>248568764</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000959683293001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9812 за поставленный товар</t>
+          <t>ОПЛАТА ПО С/Ф №371 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4802,40 +4787,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>4094000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>6545000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Mahsulot uchun to'lov, shartnoma №270/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4845,38 +4830,38 @@
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>31697000</v>
+        <v>3095000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Oydin Meva-Sabzavot MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>356850141</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000716966012001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7620 24.08.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №9132 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4886,38 +4871,38 @@
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>21922000</v>
+        <v>10727000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9624 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №1985 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4925,40 +4910,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>9957000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>2476000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Navoiy Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>237319010</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000751615296001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №88/26 ОТ 24.08.2026</t>
+          <t>Аренда помещения за сентябрь, дог. №29/22</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4966,40 +4951,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>9498000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>48034000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №266/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №1601</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5009,38 +4994,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>8497000</v>
+        <v>2610000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chust Sut AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>299289915</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000855892055001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8207 24.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №39/26 от 11.09.2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5048,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>7505000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>5146000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Navro'z Logistik MChJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>251983633</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000027244948001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5298 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №278/26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5089,40 +5074,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>6593000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>11524000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Ziyo Mebel XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>304179873</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000072850583001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №180/26 от 24.08.2026</t>
+          <t>Оплата за транспортные услуги по договору №90/26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5132,21 +5117,21 @@
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>4381000</v>
+        <v>3374000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>275041798</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000320728505001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5156,14 +5141,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №120/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8780 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5171,40 +5156,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>3228000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>4654000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №189/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №118/26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5212,40 +5197,40 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>3135000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>14126000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lazzat Sut MChJ</t>
+          <t>Bekobod Plastik AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>356521849</t>
+          <t>328991598</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000365559353001</t>
+          <t>20208000589205515001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5064 за поставленный товар</t>
+          <t>Предоплата за материалы по договор №27/26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5255,21 +5240,21 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>2749000</v>
+        <v>5882000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5279,14 +5264,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4567 24.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3168</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5295,39 +5280,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>1563000</v>
+        <v>2746000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000566813144001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5336,39 +5321,39 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>5217000</v>
+        <v>2746000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №5/26 от 24.08.2026, НДС 12%</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5378,21 +5363,21 @@
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>2636000</v>
+        <v>7188000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5402,14 +5387,14 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1700 от 25.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №13/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5417,35 +5402,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>38239000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9708)</t>
+          <t>Yulduz Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>298363380</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>16307000352556491417</t>
+          <t>20208000724494826001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-9708 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за продукцию по дог. №52/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5455,21 +5445,21 @@
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>3853000</v>
+        <v>9694000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5479,14 +5469,14 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5322 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №293 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5494,40 +5484,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>8834000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>2618000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nurafshon Qurilish Materiallari MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>255201724</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000143254582001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №252/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №92/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5535,23 +5525,23 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>31961000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>2032000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>356876449</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000968329370001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5561,14 +5551,14 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №133/26</t>
+          <t>Предоплата за товар по договору №116/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5576,40 +5566,40 @@
           <t>223</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>4275000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>37935000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Bekobod Plastik AJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>328991598</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000589205515001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №164/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №90/26</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5619,21 +5609,21 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>2922000</v>
+        <v>7175000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5643,14 +5633,14 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2204 за поставленный товар</t>
+          <t>Оплата по с/ф №2050 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5658,40 +5648,40 @@
           <t>225</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>10625000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>4461000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Namangan Oziq-ovqat Savdo MChJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>385763540</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000150313041001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3213 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №9973</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5701,38 +5691,38 @@
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>8133000</v>
+        <v>6571000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Shartnoma №296/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №1/26 от 21.09.2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5742,38 +5732,38 @@
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>2809000</v>
+        <v>4998000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6487</t>
+          <t>Оплата по счет-фактуре №1751 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5782,34 +5772,39 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>300000</v>
+        <v>3947000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5818,39 +5813,39 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>4935000</v>
+        <v>14868000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bekobod Tikuv MChJ</t>
+          <t>Sharq Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>313731901</t>
+          <t>236957552</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000075161529001</t>
+          <t>20208000472349409001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №26/26</t>
+          <t>Оплата за товары согласно счет-фактуре №6769</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5859,39 +5854,39 @@
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>9285000</v>
+        <v>1548000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000846034809001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №62/26</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5899,40 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>1588000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>4698000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Shartnoma №164/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №3068</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5942,38 +5937,38 @@
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>8515000</v>
+        <v>5463000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Zarafshon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>356876449</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000968329370001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №133/26 от 02.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №1099 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5981,40 +5976,35 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>3610000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>248568764</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-9708)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000959683293001</t>
+          <t>16307000352556491417</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3255 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Kredit shartnomasi L-2024-9708 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6022,35 +6012,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>20136000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>51358000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Yulduz Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>298363380</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000724494826001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №291</t>
+          <t>Предоплата за товар по договору №214/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6058,40 +6053,40 @@
           <t>235</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>90969000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>4980000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Saodat Poligraf MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>371369575</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000274723494001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1550</t>
+          <t>Оплата за продукцию по договору №213/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6101,38 +6096,38 @@
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>24971000</v>
+        <v>3138000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mato MChJ</t>
+          <t>Shahrisabz Moy MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>331743410</t>
+          <t>380913977</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000553436114001</t>
+          <t>20208000567012201001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9130 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2147 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6140,40 +6135,40 @@
           <t>237</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>12867000</v>
-      </c>
+      <c r="C147" s="2" t="n">
+        <v>5821000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №132/26 от 07.09.2026</t>
+          <t>Предоплата за материалы по договору №105/26</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6181,40 +6176,40 @@
           <t>238</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>4140000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>17052000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7351 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №252/26</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6222,40 +6217,40 @@
           <t>239</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>1456000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>24630000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chust Sut AJ</t>
+          <t>Ziyo Mebel XK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>299289915</t>
+          <t>304179873</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000855892055001</t>
+          <t>20208000072850583001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №30/26 от 07.09.2026</t>
+          <t>Оплата за транспортные услуги по дог. №270/26</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6263,40 +6258,40 @@
           <t>240</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>2476000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>18648000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Omad Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>228532391</t>
+          <t>376354061</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000990517963001</t>
+          <t>20208000031304153001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartn. №19/21</t>
+          <t>Предоплата за товар по договору №16/26 от 29.09.2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6306,38 +6301,38 @@
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>10479000</v>
+        <v>6666000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Yulduz Tekstil MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>298363380</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000724494826001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8612 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №9507 от 30.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6345,40 +6340,35 @@
           <t>242</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>6693000</v>
-      </c>
+      <c r="C152" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>327809139</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5163 ОТ 11.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6386,1525 +6376,59 @@
           <t>243</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>2179000</v>
-      </c>
+      <c r="C153" s="2" t="n">
+        <v>15004000</v>
+      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
+          <t>Lazzat Agro MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>327809139</t>
+          <t>385014107</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000775670122001</t>
+          <t>20208000696601229001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №51/26 от 11.09.2026</t>
+          <t>Оплата за сырье по дог. №272/26 от 30.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>77229000</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9259</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>989919000</v>
+      </c>
+      <c r="D154" s="4" t="n">
+        <v>997219000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>7386000</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №7040 от 14.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>12879000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Saodat Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>371369575</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000274723494001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №1058</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>1837000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>275041798</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000320728505001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №206/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>2746000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Уплата социального налога за август</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>2746000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>НДФЛ за август 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>4678000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>275041798</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000320728505001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №107/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>2497000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Navro'z Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>251983633</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000027244948001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №5752 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>14094000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Mato MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>331743410</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000553436114001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №6805 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>1374000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №7220 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>21899000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Saodat Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>371369575</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000274723494001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №149/26 от 17.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>6858000</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №267/26 от 18.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>2411000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №5477 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>29739000</v>
-      </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Bekobod Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>313731901</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000075161529001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №121/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>6304000</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>275041798</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000320728505001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №7834 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n">
-        <v>6020000</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №175/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>3286000</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №86/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>2580000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>275041798</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000320728505001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №1756 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>2565000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Namangan Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>385763540</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000150313041001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Оплата по с/ф №5427 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>4210000</v>
-      </c>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>52358000</v>
-      </c>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Saodat Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>371369575</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000274723494001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №513</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>2976000</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>275041798</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000320728505001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №251/26 от 22.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>10070000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Saodat Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>371369575</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000274723494001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №4935</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n">
-        <v>46827000</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №1772 от 24.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n"/>
-      <c r="D178" s="2" t="n">
-        <v>5570000</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №145/26 ОТ 24.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>3887000</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Afrosiyob Agro Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>248568764</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000959683293001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №1983 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-9708)</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>16307000352556491417</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2024-9708 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>43228000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Angren Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>394753331</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000158343630001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №1219</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n">
-        <v>4636000</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Namangan Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>385763540</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000150313041001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №77/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n">
-        <v>3160000</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Afrosiyob Agro Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>248568764</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000959683293001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №95/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n">
-        <v>1712000</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №280/26 ОТ 28.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n"/>
-      <c r="D185" s="2" t="n">
-        <v>1474000</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №4448 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>1548000</v>
-      </c>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000566813144001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="n"/>
-      <c r="D187" s="2" t="n">
-        <v>64950000</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Bunyodkor Ip-Kalava AJ</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>327809139</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000775670122001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №187/26 от 29.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D188" s="2" t="n"/>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Navbahor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="n">
-        <v>28173000</v>
-      </c>
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Denov Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>303480905</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000823043299001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №223/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="n">
-        <v>1014879000</v>
-      </c>
-      <c r="D190" s="4" t="n">
-        <v>1022179000</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C191" s="4" t="n">
+      <c r="C155" s="4" t="n">
         <v>59200000</v>
       </c>
-      <c r="D191" s="4" t="n"/>
+      <c r="D155" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
